--- a/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-07-2026-10-07.xlsx
+++ b/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-07-2026-10-07.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\SUIVI SERVICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\PROJETS\NOUVEAUX_RECAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBBB2D9F-6050-4476-B922-DC72BEBF9061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07B20FE3-466B-42D4-B2F7-F4908B1771D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{07EF5ACC-C662-4A3C-B359-46EA478772EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{7FBB805B-D8E0-43E0-BB54-0BBB18941F4C}"/>
   </bookViews>
   <sheets>
     <sheet name="category-sales-summary-2026-10-" sheetId="1" r:id="rId1"/>
@@ -955,7 +955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130FC887-1D9C-46B9-9FBB-5B9E74CFEC02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AABA0B9-170C-4BFA-B0C0-38A056D0FC3E}">
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
